--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123815157</v>
+        <v>123830609</v>
       </c>
       <c r="B2" t="n">
-        <v>94796</v>
+        <v>100680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2808</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668021</v>
+        <v>667970</v>
       </c>
       <c r="R2" t="n">
-        <v>6984842</v>
+        <v>6984746</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,16 +780,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,6 +794,1475 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123821176</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>667999</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6984703</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123821223</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57503</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>668007</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6984841</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123815157</v>
+      </c>
+      <c r="B5" t="n">
+        <v>94796</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2808</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grov husmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum pyrenaicum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spruce) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>668021</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6984842</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123830634</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100680</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>667971</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6984715</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123830174</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100680</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>668067</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6984782</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123830564</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100680</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>667999</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6984717</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123830239</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100680</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>668068</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6984751</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123821192</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>668023</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6984811</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123830363</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100680</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>668042</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6984719</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123830526</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100680</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>668012</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6984748</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123821283</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>668051</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6984812</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123821271</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>668007</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6984841</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123830609</v>
+        <v>123830239</v>
       </c>
       <c r="B2" t="n">
         <v>100680</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667970</v>
+        <v>668068</v>
       </c>
       <c r="R2" t="n">
-        <v>6984746</v>
+        <v>6984751</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123821176</v>
+        <v>123821192</v>
       </c>
       <c r="B3" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667999</v>
+        <v>668023</v>
       </c>
       <c r="R3" t="n">
-        <v>6984703</v>
+        <v>6984811</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +903,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123821223</v>
+        <v>123830526</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>100680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,43 +936,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668007</v>
+        <v>668012</v>
       </c>
       <c r="R4" t="n">
-        <v>6984841</v>
+        <v>6984748</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,14 +1046,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123815157</v>
+        <v>123830174</v>
       </c>
       <c r="B5" t="n">
-        <v>94796</v>
+        <v>100680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1057,34 +1062,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2808</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668021</v>
+        <v>668067</v>
       </c>
       <c r="R5" t="n">
-        <v>6984842</v>
+        <v>6984782</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,16 +1151,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123830634</v>
+        <v>123821176</v>
       </c>
       <c r="B6" t="n">
         <v>100680</v>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>667971</v>
+        <v>667999</v>
       </c>
       <c r="R6" t="n">
-        <v>6984715</v>
+        <v>6984703</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,11 +1269,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,14 +1285,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123830174</v>
+        <v>123815157</v>
       </c>
       <c r="B7" t="n">
-        <v>100680</v>
+        <v>94802</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1306,39 +1301,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>2808</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668067</v>
+        <v>668021</v>
       </c>
       <c r="R7" t="n">
-        <v>6984782</v>
+        <v>6984842</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,6 +1385,16 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123830564</v>
+        <v>123830609</v>
       </c>
       <c r="B8" t="n">
         <v>100680</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>667999</v>
+        <v>667970</v>
       </c>
       <c r="R8" t="n">
-        <v>6984717</v>
+        <v>6984746</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123830239</v>
+        <v>123830564</v>
       </c>
       <c r="B9" t="n">
         <v>100680</v>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668068</v>
+        <v>667999</v>
       </c>
       <c r="R9" t="n">
-        <v>6984751</v>
+        <v>6984717</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,10 +1656,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123821192</v>
+        <v>123830634</v>
       </c>
       <c r="B10" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668023</v>
+        <v>667971</v>
       </c>
       <c r="R10" t="n">
-        <v>6984811</v>
+        <v>6984715</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,12 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,7 +1760,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1905,7 +1900,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123830526</v>
+        <v>123821283</v>
       </c>
       <c r="B12" t="n">
         <v>100680</v>
@@ -1939,21 +1934,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668012</v>
+        <v>668051</v>
       </c>
       <c r="R12" t="n">
-        <v>6984748</v>
+        <v>6984812</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1985,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1995,7 +1985,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123821283</v>
+        <v>123821271</v>
       </c>
       <c r="B13" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2061,16 +2051,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668051</v>
+        <v>668007</v>
       </c>
       <c r="R13" t="n">
-        <v>6984812</v>
+        <v>6984841</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2102,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123821271</v>
+        <v>123821223</v>
       </c>
       <c r="B14" t="n">
-        <v>100662</v>
+        <v>57506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2156,36 +2151,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2235,6 +2230,11 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123830239</v>
+        <v>123830634</v>
       </c>
       <c r="B2" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668068</v>
+        <v>667971</v>
       </c>
       <c r="R2" t="n">
-        <v>6984751</v>
+        <v>6984715</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123821192</v>
+        <v>123821283</v>
       </c>
       <c r="B3" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,21 +831,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668023</v>
+        <v>668051</v>
       </c>
       <c r="R3" t="n">
-        <v>6984811</v>
+        <v>6984812</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +896,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123830526</v>
+        <v>123830239</v>
       </c>
       <c r="B4" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668012</v>
+        <v>668068</v>
       </c>
       <c r="R4" t="n">
-        <v>6984748</v>
+        <v>6984751</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123830174</v>
+        <v>123830363</v>
       </c>
       <c r="B5" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668067</v>
+        <v>668042</v>
       </c>
       <c r="R5" t="n">
-        <v>6984782</v>
+        <v>6984719</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123821176</v>
+        <v>123821271</v>
       </c>
       <c r="B6" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>667999</v>
+        <v>668007</v>
       </c>
       <c r="R6" t="n">
-        <v>6984703</v>
+        <v>6984841</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,6 +1259,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1285,14 +1280,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123815157</v>
+        <v>123821176</v>
       </c>
       <c r="B7" t="n">
-        <v>94802</v>
+        <v>100682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1301,34 +1296,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2808</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668021</v>
+        <v>667999</v>
       </c>
       <c r="R7" t="n">
-        <v>6984842</v>
+        <v>6984703</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,21 +1381,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1412,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123830609</v>
+        <v>123821223</v>
       </c>
       <c r="B8" t="n">
-        <v>100680</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1424,43 +1409,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>667970</v>
+        <v>668007</v>
       </c>
       <c r="R8" t="n">
-        <v>6984746</v>
+        <v>6984841</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1492,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1487,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,14 +1524,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123830564</v>
+        <v>123815157</v>
       </c>
       <c r="B9" t="n">
-        <v>100680</v>
+        <v>94804</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1550,39 +1540,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2808</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>667999</v>
+        <v>668021</v>
       </c>
       <c r="R9" t="n">
-        <v>6984717</v>
+        <v>6984842</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1614,7 +1599,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1609,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,6 +1624,16 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1656,10 +1651,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123830634</v>
+        <v>123830526</v>
       </c>
       <c r="B10" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>667971</v>
+        <v>668012</v>
       </c>
       <c r="R10" t="n">
-        <v>6984715</v>
+        <v>6984748</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1736,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1741,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123830363</v>
+        <v>123830564</v>
       </c>
       <c r="B11" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668042</v>
+        <v>667999</v>
       </c>
       <c r="R11" t="n">
-        <v>6984719</v>
+        <v>6984717</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1858,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123821283</v>
+        <v>123830174</v>
       </c>
       <c r="B12" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,16 +1929,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668051</v>
+        <v>668067</v>
       </c>
       <c r="R12" t="n">
-        <v>6984812</v>
+        <v>6984782</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123821271</v>
+        <v>123830609</v>
       </c>
       <c r="B13" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668007</v>
+        <v>667970</v>
       </c>
       <c r="R13" t="n">
-        <v>6984841</v>
+        <v>6984746</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123821223</v>
+        <v>123821192</v>
       </c>
       <c r="B14" t="n">
-        <v>57506</v>
+        <v>100682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,43 +2151,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668007</v>
+        <v>668023</v>
       </c>
       <c r="R14" t="n">
-        <v>6984841</v>
+        <v>6984811</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -1895,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123830174</v>
+        <v>123830609</v>
       </c>
       <c r="B12" t="n">
         <v>100682</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668067</v>
+        <v>667970</v>
       </c>
       <c r="R12" t="n">
-        <v>6984782</v>
+        <v>6984746</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,7 +2017,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123830609</v>
+        <v>123830174</v>
       </c>
       <c r="B13" t="n">
         <v>100682</v>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>667970</v>
+        <v>668067</v>
       </c>
       <c r="R13" t="n">
-        <v>6984746</v>
+        <v>6984782</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -1895,7 +1895,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123830609</v>
+        <v>123830174</v>
       </c>
       <c r="B12" t="n">
         <v>100682</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>667970</v>
+        <v>668067</v>
       </c>
       <c r="R12" t="n">
-        <v>6984746</v>
+        <v>6984782</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,7 +2017,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123830174</v>
+        <v>123830609</v>
       </c>
       <c r="B13" t="n">
         <v>100682</v>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668067</v>
+        <v>667970</v>
       </c>
       <c r="R13" t="n">
-        <v>6984782</v>
+        <v>6984746</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123830634</v>
+        <v>123815157</v>
       </c>
       <c r="B2" t="n">
-        <v>100682</v>
+        <v>95312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2808</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667971</v>
+        <v>668021</v>
       </c>
       <c r="R2" t="n">
-        <v>6984715</v>
+        <v>6984842</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +775,16 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123821283</v>
+        <v>123830564</v>
       </c>
       <c r="B3" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,16 +836,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668051</v>
+        <v>667999</v>
       </c>
       <c r="R3" t="n">
-        <v>6984812</v>
+        <v>6984717</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123830239</v>
+        <v>123830634</v>
       </c>
       <c r="B4" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668068</v>
+        <v>667971</v>
       </c>
       <c r="R4" t="n">
-        <v>6984751</v>
+        <v>6984715</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123830363</v>
+        <v>123821192</v>
       </c>
       <c r="B5" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668042</v>
+        <v>668023</v>
       </c>
       <c r="R5" t="n">
-        <v>6984719</v>
+        <v>6984811</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1116,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,7 +1155,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1158,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123821271</v>
+        <v>123830174</v>
       </c>
       <c r="B6" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,10 +1218,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668007</v>
+        <v>668067</v>
       </c>
       <c r="R6" t="n">
-        <v>6984841</v>
+        <v>6984782</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,7 +1253,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1263,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123821176</v>
+        <v>123830239</v>
       </c>
       <c r="B7" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1325,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>667999</v>
+        <v>668068</v>
       </c>
       <c r="R7" t="n">
-        <v>6984703</v>
+        <v>6984751</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1360,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1385,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,6 +1396,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123821223</v>
+        <v>123830363</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,43 +1429,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668007</v>
+        <v>668042</v>
       </c>
       <c r="R8" t="n">
-        <v>6984841</v>
+        <v>6984719</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1477,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,12 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1524,50 +1539,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123815157</v>
+        <v>123821223</v>
       </c>
       <c r="B9" t="n">
-        <v>94804</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2808</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668021</v>
+        <v>668007</v>
       </c>
       <c r="R9" t="n">
-        <v>6984842</v>
+        <v>6984841</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1599,7 +1619,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1609,7 +1629,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,16 +1649,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1651,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123830526</v>
+        <v>123821176</v>
       </c>
       <c r="B10" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1696,10 +1711,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668012</v>
+        <v>667999</v>
       </c>
       <c r="R10" t="n">
-        <v>6984748</v>
+        <v>6984703</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1731,7 +1746,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1741,7 +1756,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,11 +1767,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1773,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123830564</v>
+        <v>123830609</v>
       </c>
       <c r="B11" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,10 +1828,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>667999</v>
+        <v>667970</v>
       </c>
       <c r="R11" t="n">
-        <v>6984717</v>
+        <v>6984746</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1853,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1873,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,10 +1905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123830174</v>
+        <v>123821271</v>
       </c>
       <c r="B12" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1940,10 +1950,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668067</v>
+        <v>668007</v>
       </c>
       <c r="R12" t="n">
-        <v>6984782</v>
+        <v>6984841</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,7 +1985,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1995,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,10 +2027,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123830609</v>
+        <v>123830526</v>
       </c>
       <c r="B13" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2062,10 +2072,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>667970</v>
+        <v>668012</v>
       </c>
       <c r="R13" t="n">
-        <v>6984746</v>
+        <v>6984748</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2097,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2117,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123821192</v>
+        <v>123821283</v>
       </c>
       <c r="B14" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,21 +2183,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668023</v>
+        <v>668051</v>
       </c>
       <c r="R14" t="n">
-        <v>6984811</v>
+        <v>6984812</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2219,7 +2224,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,12 +2234,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,50 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123815157</v>
+        <v>123821223</v>
       </c>
       <c r="B2" t="n">
-        <v>95312</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2808</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668021</v>
+        <v>668007</v>
       </c>
       <c r="R2" t="n">
-        <v>6984842</v>
+        <v>6984841</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,16 +785,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123830564</v>
+        <v>123830634</v>
       </c>
       <c r="B3" t="n">
         <v>100257</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667999</v>
+        <v>667971</v>
       </c>
       <c r="R3" t="n">
-        <v>6984717</v>
+        <v>6984715</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123830634</v>
+        <v>123830609</v>
       </c>
       <c r="B4" t="n">
         <v>100257</v>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667971</v>
+        <v>667970</v>
       </c>
       <c r="R4" t="n">
-        <v>6984715</v>
+        <v>6984746</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123821192</v>
+        <v>123821271</v>
       </c>
       <c r="B5" t="n">
         <v>100257</v>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668023</v>
+        <v>668007</v>
       </c>
       <c r="R5" t="n">
-        <v>6984811</v>
+        <v>6984841</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,7 +1150,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,14 +1168,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123830174</v>
+        <v>123815157</v>
       </c>
       <c r="B6" t="n">
-        <v>100257</v>
+        <v>95312</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1189,39 +1184,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2808</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668067</v>
+        <v>668021</v>
       </c>
       <c r="R6" t="n">
-        <v>6984782</v>
+        <v>6984842</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1253,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1263,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,6 +1268,16 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1295,7 +1295,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123830239</v>
+        <v>123821176</v>
       </c>
       <c r="B7" t="n">
         <v>100257</v>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668068</v>
+        <v>667999</v>
       </c>
       <c r="R7" t="n">
-        <v>6984751</v>
+        <v>6984703</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,11 +1396,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1417,7 +1412,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123830363</v>
+        <v>123821192</v>
       </c>
       <c r="B8" t="n">
         <v>100257</v>
@@ -1462,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668042</v>
+        <v>668023</v>
       </c>
       <c r="R8" t="n">
-        <v>6984719</v>
+        <v>6984811</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1497,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,7 +1502,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123821223</v>
+        <v>123830526</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,43 +1551,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668007</v>
+        <v>668012</v>
       </c>
       <c r="R9" t="n">
-        <v>6984841</v>
+        <v>6984748</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1629,12 +1629,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,7 +1661,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123821176</v>
+        <v>123830174</v>
       </c>
       <c r="B10" t="n">
         <v>100257</v>
@@ -1711,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>667999</v>
+        <v>668067</v>
       </c>
       <c r="R10" t="n">
-        <v>6984703</v>
+        <v>6984782</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1746,7 +1741,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,7 +1751,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,6 +1762,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1783,7 +1783,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123830609</v>
+        <v>123821283</v>
       </c>
       <c r="B11" t="n">
         <v>100257</v>
@@ -1817,21 +1817,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>667970</v>
+        <v>668051</v>
       </c>
       <c r="R11" t="n">
-        <v>6984746</v>
+        <v>6984812</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,7 +1868,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,7 +1900,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123821271</v>
+        <v>123830239</v>
       </c>
       <c r="B12" t="n">
         <v>100257</v>
@@ -1950,10 +1945,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668007</v>
+        <v>668068</v>
       </c>
       <c r="R12" t="n">
-        <v>6984841</v>
+        <v>6984751</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1985,7 +1980,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1995,7 +1990,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,7 +2022,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123830526</v>
+        <v>123830363</v>
       </c>
       <c r="B13" t="n">
         <v>100257</v>
@@ -2072,10 +2067,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668012</v>
+        <v>668042</v>
       </c>
       <c r="R13" t="n">
-        <v>6984748</v>
+        <v>6984719</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2149,7 +2144,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123821283</v>
+        <v>123830564</v>
       </c>
       <c r="B14" t="n">
         <v>100257</v>
@@ -2183,16 +2178,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668051</v>
+        <v>667999</v>
       </c>
       <c r="R14" t="n">
-        <v>6984812</v>
+        <v>6984717</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123821223</v>
+        <v>123830609</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668007</v>
+        <v>667970</v>
       </c>
       <c r="R2" t="n">
-        <v>6984841</v>
+        <v>6984746</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123830634</v>
+        <v>123821176</v>
       </c>
       <c r="B3" t="n">
         <v>100257</v>
@@ -847,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667971</v>
+        <v>667999</v>
       </c>
       <c r="R3" t="n">
-        <v>6984715</v>
+        <v>6984703</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,11 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123830609</v>
+        <v>123830363</v>
       </c>
       <c r="B4" t="n">
         <v>100257</v>
@@ -969,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667970</v>
+        <v>668042</v>
       </c>
       <c r="R4" t="n">
-        <v>6984746</v>
+        <v>6984719</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123821271</v>
+        <v>123830634</v>
       </c>
       <c r="B5" t="n">
         <v>100257</v>
@@ -1091,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668007</v>
+        <v>667971</v>
       </c>
       <c r="R5" t="n">
-        <v>6984841</v>
+        <v>6984715</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,14 +1158,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123815157</v>
+        <v>123830526</v>
       </c>
       <c r="B6" t="n">
-        <v>95312</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1184,34 +1174,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2808</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668021</v>
+        <v>668012</v>
       </c>
       <c r="R6" t="n">
-        <v>6984842</v>
+        <v>6984748</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,16 +1263,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1295,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123821176</v>
+        <v>123830174</v>
       </c>
       <c r="B7" t="n">
         <v>100257</v>
@@ -1340,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>667999</v>
+        <v>668067</v>
       </c>
       <c r="R7" t="n">
-        <v>6984703</v>
+        <v>6984782</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1375,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1385,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,6 +1381,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1412,14 +1402,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123821192</v>
+        <v>123815157</v>
       </c>
       <c r="B8" t="n">
-        <v>100257</v>
+        <v>95312</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1428,39 +1418,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>2808</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668023</v>
+        <v>668021</v>
       </c>
       <c r="R8" t="n">
-        <v>6984811</v>
+        <v>6984842</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1492,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,12 +1487,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,7 +1501,17 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123830526</v>
+        <v>123821223</v>
       </c>
       <c r="B9" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,43 +1541,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668012</v>
+        <v>668007</v>
       </c>
       <c r="R9" t="n">
-        <v>6984748</v>
+        <v>6984841</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1619,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1629,7 +1619,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,7 +1656,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123830174</v>
+        <v>123830239</v>
       </c>
       <c r="B10" t="n">
         <v>100257</v>
@@ -1706,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668067</v>
+        <v>668068</v>
       </c>
       <c r="R10" t="n">
-        <v>6984782</v>
+        <v>6984751</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1741,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1751,7 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,7 +1778,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123821283</v>
+        <v>123821192</v>
       </c>
       <c r="B11" t="n">
         <v>100257</v>
@@ -1817,16 +1812,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668051</v>
+        <v>668023</v>
       </c>
       <c r="R11" t="n">
-        <v>6984812</v>
+        <v>6984811</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,7 +1868,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,7 +1887,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1900,7 +1905,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123830239</v>
+        <v>123830564</v>
       </c>
       <c r="B12" t="n">
         <v>100257</v>
@@ -1945,10 +1950,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668068</v>
+        <v>667999</v>
       </c>
       <c r="R12" t="n">
-        <v>6984751</v>
+        <v>6984717</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1980,7 +1985,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1990,7 +1995,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2022,7 +2027,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123830363</v>
+        <v>123821283</v>
       </c>
       <c r="B13" t="n">
         <v>100257</v>
@@ -2056,21 +2061,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668042</v>
+        <v>668051</v>
       </c>
       <c r="R13" t="n">
-        <v>6984719</v>
+        <v>6984812</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,7 +2144,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123830564</v>
+        <v>123821271</v>
       </c>
       <c r="B14" t="n">
         <v>100257</v>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667999</v>
+        <v>668007</v>
       </c>
       <c r="R14" t="n">
-        <v>6984717</v>
+        <v>6984841</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123830609</v>
+        <v>123830564</v>
       </c>
       <c r="B2" t="n">
         <v>100257</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667970</v>
+        <v>667999</v>
       </c>
       <c r="R2" t="n">
-        <v>6984746</v>
+        <v>6984717</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123821176</v>
+        <v>123830609</v>
       </c>
       <c r="B3" t="n">
         <v>100257</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667999</v>
+        <v>667970</v>
       </c>
       <c r="R3" t="n">
-        <v>6984703</v>
+        <v>6984746</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,6 +898,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,7 +919,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123830363</v>
+        <v>123830174</v>
       </c>
       <c r="B4" t="n">
         <v>100257</v>
@@ -959,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668042</v>
+        <v>668067</v>
       </c>
       <c r="R4" t="n">
-        <v>6984719</v>
+        <v>6984782</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1158,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123830526</v>
+        <v>123821223</v>
       </c>
       <c r="B6" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,43 +1175,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668012</v>
+        <v>668007</v>
       </c>
       <c r="R6" t="n">
-        <v>6984748</v>
+        <v>6984841</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1290,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123830174</v>
+        <v>123830526</v>
       </c>
       <c r="B7" t="n">
         <v>100257</v>
@@ -1325,10 +1335,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668067</v>
+        <v>668012</v>
       </c>
       <c r="R7" t="n">
-        <v>6984782</v>
+        <v>6984748</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1360,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1380,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1529,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123821223</v>
+        <v>123821192</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,43 +1551,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668007</v>
+        <v>668023</v>
       </c>
       <c r="R9" t="n">
-        <v>6984841</v>
+        <v>6984811</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1609,7 +1619,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1619,12 +1629,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,7 +1648,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1656,7 +1666,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123830239</v>
+        <v>123821176</v>
       </c>
       <c r="B10" t="n">
         <v>100257</v>
@@ -1701,10 +1711,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668068</v>
+        <v>667999</v>
       </c>
       <c r="R10" t="n">
-        <v>6984751</v>
+        <v>6984703</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1736,7 +1746,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1756,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,11 +1767,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1778,7 +1783,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123821192</v>
+        <v>123830363</v>
       </c>
       <c r="B11" t="n">
         <v>100257</v>
@@ -1823,10 +1828,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668023</v>
+        <v>668042</v>
       </c>
       <c r="R11" t="n">
-        <v>6984811</v>
+        <v>6984719</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1858,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,12 +1873,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1905,7 +1905,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123830564</v>
+        <v>123830239</v>
       </c>
       <c r="B12" t="n">
         <v>100257</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>667999</v>
+        <v>668068</v>
       </c>
       <c r="R12" t="n">
-        <v>6984717</v>
+        <v>6984751</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,7 +2027,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123821283</v>
+        <v>123821271</v>
       </c>
       <c r="B13" t="n">
         <v>100257</v>
@@ -2061,16 +2061,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668051</v>
+        <v>668007</v>
       </c>
       <c r="R13" t="n">
-        <v>6984812</v>
+        <v>6984841</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2102,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,7 +2117,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,7 +2149,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123821271</v>
+        <v>123821283</v>
       </c>
       <c r="B14" t="n">
         <v>100257</v>
@@ -2178,21 +2183,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668007</v>
+        <v>668051</v>
       </c>
       <c r="R14" t="n">
-        <v>6984841</v>
+        <v>6984812</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123821223</v>
+        <v>123830526</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,43 +1175,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668007</v>
+        <v>668012</v>
       </c>
       <c r="R6" t="n">
-        <v>6984841</v>
+        <v>6984748</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123830526</v>
+        <v>123821223</v>
       </c>
       <c r="B7" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,43 +1297,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668012</v>
+        <v>668007</v>
       </c>
       <c r="R7" t="n">
-        <v>6984748</v>
+        <v>6984841</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1375,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123830564</v>
+        <v>123821271</v>
       </c>
       <c r="B2" t="n">
         <v>100257</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667999</v>
+        <v>668007</v>
       </c>
       <c r="R2" t="n">
-        <v>6984717</v>
+        <v>6984841</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123830609</v>
+        <v>123821223</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,43 +809,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667970</v>
+        <v>668007</v>
       </c>
       <c r="R3" t="n">
-        <v>6984746</v>
+        <v>6984841</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123830174</v>
+        <v>123821176</v>
       </c>
       <c r="B4" t="n">
         <v>100257</v>
@@ -964,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668067</v>
+        <v>667999</v>
       </c>
       <c r="R4" t="n">
-        <v>6984782</v>
+        <v>6984703</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -999,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,11 +1025,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1163,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123830526</v>
+        <v>123821283</v>
       </c>
       <c r="B6" t="n">
         <v>100257</v>
@@ -1197,21 +1197,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668012</v>
+        <v>668051</v>
       </c>
       <c r="R6" t="n">
-        <v>6984748</v>
+        <v>6984812</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1243,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,55 +1280,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123821223</v>
+        <v>123815157</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>95312</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2808</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668007</v>
+        <v>668021</v>
       </c>
       <c r="R7" t="n">
-        <v>6984841</v>
+        <v>6984842</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1365,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,12 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,6 +1380,16 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,14 +1407,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123815157</v>
+        <v>123830609</v>
       </c>
       <c r="B8" t="n">
-        <v>95312</v>
+        <v>100257</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1428,34 +1423,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2808</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668021</v>
+        <v>667970</v>
       </c>
       <c r="R8" t="n">
-        <v>6984842</v>
+        <v>6984746</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,16 +1512,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,7 +1529,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123821192</v>
+        <v>123830564</v>
       </c>
       <c r="B9" t="n">
         <v>100257</v>
@@ -1584,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668023</v>
+        <v>667999</v>
       </c>
       <c r="R9" t="n">
-        <v>6984811</v>
+        <v>6984717</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1619,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1629,12 +1619,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,7 +1633,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,7 +1651,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123821176</v>
+        <v>123830239</v>
       </c>
       <c r="B10" t="n">
         <v>100257</v>
@@ -1711,10 +1696,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>667999</v>
+        <v>668068</v>
       </c>
       <c r="R10" t="n">
-        <v>6984703</v>
+        <v>6984751</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1746,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1756,7 +1741,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,6 +1752,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1783,7 +1773,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123830363</v>
+        <v>123821192</v>
       </c>
       <c r="B11" t="n">
         <v>100257</v>
@@ -1828,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668042</v>
+        <v>668023</v>
       </c>
       <c r="R11" t="n">
-        <v>6984719</v>
+        <v>6984811</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1863,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,7 +1863,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,7 +1882,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1905,7 +1900,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123830239</v>
+        <v>123830363</v>
       </c>
       <c r="B12" t="n">
         <v>100257</v>
@@ -1950,10 +1945,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668068</v>
+        <v>668042</v>
       </c>
       <c r="R12" t="n">
-        <v>6984751</v>
+        <v>6984719</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1985,7 +1980,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1995,7 +1990,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,7 +2022,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123821271</v>
+        <v>123830526</v>
       </c>
       <c r="B13" t="n">
         <v>100257</v>
@@ -2072,10 +2067,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668007</v>
+        <v>668012</v>
       </c>
       <c r="R13" t="n">
-        <v>6984841</v>
+        <v>6984748</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2107,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2149,7 +2144,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123821283</v>
+        <v>123830174</v>
       </c>
       <c r="B14" t="n">
         <v>100257</v>
@@ -2183,16 +2178,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668051</v>
+        <v>668067</v>
       </c>
       <c r="R14" t="n">
-        <v>6984812</v>
+        <v>6984782</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123815157</v>
+        <v>123821283</v>
       </c>
       <c r="B2" t="n">
-        <v>95334</v>
+        <v>100279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2808</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668021</v>
+        <v>668051</v>
       </c>
       <c r="R2" t="n">
-        <v>6984842</v>
+        <v>6984812</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,16 +775,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123830526</v>
+        <v>123830363</v>
       </c>
       <c r="B3" t="n">
         <v>100279</v>
@@ -847,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668012</v>
+        <v>668042</v>
       </c>
       <c r="R3" t="n">
-        <v>6984748</v>
+        <v>6984719</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -924,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123830634</v>
+        <v>123821223</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,43 +926,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667971</v>
+        <v>668007</v>
       </c>
       <c r="R4" t="n">
-        <v>6984715</v>
+        <v>6984841</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123830363</v>
+        <v>123821192</v>
       </c>
       <c r="B5" t="n">
         <v>100279</v>
@@ -1091,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668042</v>
+        <v>668023</v>
       </c>
       <c r="R5" t="n">
-        <v>6984719</v>
+        <v>6984811</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1131,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123830174</v>
+        <v>123830609</v>
       </c>
       <c r="B6" t="n">
         <v>100279</v>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668067</v>
+        <v>667970</v>
       </c>
       <c r="R6" t="n">
-        <v>6984782</v>
+        <v>6984746</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,7 +1290,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123830564</v>
+        <v>123830634</v>
       </c>
       <c r="B7" t="n">
         <v>100279</v>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>667999</v>
+        <v>667971</v>
       </c>
       <c r="R7" t="n">
-        <v>6984717</v>
+        <v>6984715</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,7 +1412,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123821271</v>
+        <v>123830239</v>
       </c>
       <c r="B8" t="n">
         <v>100279</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668007</v>
+        <v>668068</v>
       </c>
       <c r="R8" t="n">
-        <v>6984841</v>
+        <v>6984751</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123830239</v>
+        <v>123830174</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668068</v>
+        <v>668067</v>
       </c>
       <c r="R9" t="n">
-        <v>6984751</v>
+        <v>6984782</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123830609</v>
+        <v>123830526</v>
       </c>
       <c r="B10" t="n">
         <v>100279</v>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>667970</v>
+        <v>668012</v>
       </c>
       <c r="R10" t="n">
-        <v>6984746</v>
+        <v>6984748</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,7 +1778,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123821176</v>
+        <v>123821271</v>
       </c>
       <c r="B11" t="n">
         <v>100279</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>667999</v>
+        <v>668007</v>
       </c>
       <c r="R11" t="n">
-        <v>6984703</v>
+        <v>6984841</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1879,6 +1879,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1895,55 +1900,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123821223</v>
+        <v>123815157</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>95334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2808</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668007</v>
+        <v>668021</v>
       </c>
       <c r="R12" t="n">
-        <v>6984841</v>
+        <v>6984842</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,12 +1985,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2005,6 +2000,16 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2022,7 +2027,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123821192</v>
+        <v>123830564</v>
       </c>
       <c r="B13" t="n">
         <v>100279</v>
@@ -2067,10 +2072,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668023</v>
+        <v>667999</v>
       </c>
       <c r="R13" t="n">
-        <v>6984811</v>
+        <v>6984717</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2102,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2112,12 +2117,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123821283</v>
+        <v>123821176</v>
       </c>
       <c r="B14" t="n">
         <v>100279</v>
@@ -2183,16 +2183,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668051</v>
+        <v>667999</v>
       </c>
       <c r="R14" t="n">
-        <v>6984812</v>
+        <v>6984703</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2224,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2234,7 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2245,11 +2250,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123821283</v>
+        <v>123830634</v>
       </c>
       <c r="B2" t="n">
         <v>100279</v>
@@ -709,16 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668051</v>
+        <v>667971</v>
       </c>
       <c r="R2" t="n">
-        <v>6984812</v>
+        <v>6984715</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,14 +797,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123830363</v>
+        <v>123815157</v>
       </c>
       <c r="B3" t="n">
-        <v>100279</v>
+        <v>95334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -808,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2808</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668042</v>
+        <v>668021</v>
       </c>
       <c r="R3" t="n">
-        <v>6984719</v>
+        <v>6984842</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,6 +897,16 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123821223</v>
+        <v>123830363</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,43 +936,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668007</v>
+        <v>668042</v>
       </c>
       <c r="R4" t="n">
-        <v>6984841</v>
+        <v>6984719</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -994,7 +1004,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1046,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123821192</v>
+        <v>123830174</v>
       </c>
       <c r="B5" t="n">
         <v>100279</v>
@@ -1086,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668023</v>
+        <v>668067</v>
       </c>
       <c r="R5" t="n">
-        <v>6984811</v>
+        <v>6984782</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1121,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,12 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123830609</v>
+        <v>123821176</v>
       </c>
       <c r="B6" t="n">
         <v>100279</v>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>667970</v>
+        <v>667999</v>
       </c>
       <c r="R6" t="n">
-        <v>6984746</v>
+        <v>6984703</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,11 +1269,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,7 +1285,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123830634</v>
+        <v>123821192</v>
       </c>
       <c r="B7" t="n">
         <v>100279</v>
@@ -1335,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>667971</v>
+        <v>668023</v>
       </c>
       <c r="R7" t="n">
-        <v>6984715</v>
+        <v>6984811</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1375,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123830239</v>
+        <v>123830526</v>
       </c>
       <c r="B8" t="n">
         <v>100279</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668068</v>
+        <v>668012</v>
       </c>
       <c r="R8" t="n">
-        <v>6984751</v>
+        <v>6984748</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123830174</v>
+        <v>123830609</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668067</v>
+        <v>667970</v>
       </c>
       <c r="R9" t="n">
-        <v>6984782</v>
+        <v>6984746</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123830526</v>
+        <v>123821271</v>
       </c>
       <c r="B10" t="n">
         <v>100279</v>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668012</v>
+        <v>668007</v>
       </c>
       <c r="R10" t="n">
-        <v>6984748</v>
+        <v>6984841</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,7 +1778,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123821271</v>
+        <v>123830564</v>
       </c>
       <c r="B11" t="n">
         <v>100279</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668007</v>
+        <v>667999</v>
       </c>
       <c r="R11" t="n">
-        <v>6984841</v>
+        <v>6984717</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,14 +1900,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123815157</v>
+        <v>123821283</v>
       </c>
       <c r="B12" t="n">
-        <v>95334</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1916,21 +1916,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2808</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668021</v>
+        <v>668051</v>
       </c>
       <c r="R12" t="n">
-        <v>6984842</v>
+        <v>6984812</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2000,16 +2000,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2027,7 +2017,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123830564</v>
+        <v>123830239</v>
       </c>
       <c r="B13" t="n">
         <v>100279</v>
@@ -2072,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>667999</v>
+        <v>668068</v>
       </c>
       <c r="R13" t="n">
-        <v>6984717</v>
+        <v>6984751</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2107,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2149,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123821176</v>
+        <v>123821223</v>
       </c>
       <c r="B14" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2161,43 +2151,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>667999</v>
+        <v>668007</v>
       </c>
       <c r="R14" t="n">
-        <v>6984703</v>
+        <v>6984841</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2229,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2229,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2250,6 +2245,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">

--- a/artfynd/A 11972-2025 artfynd.xlsx
+++ b/artfynd/A 11972-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123830634</v>
+        <v>123821192</v>
       </c>
       <c r="B2" t="n">
         <v>100279</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667971</v>
+        <v>668023</v>
       </c>
       <c r="R2" t="n">
-        <v>6984715</v>
+        <v>6984811</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,14 +802,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123815157</v>
+        <v>123830634</v>
       </c>
       <c r="B3" t="n">
-        <v>95334</v>
+        <v>100279</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -813,34 +818,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2808</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grov husmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum pyrenaicum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spruce) M.Fleisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668021</v>
+        <v>667971</v>
       </c>
       <c r="R3" t="n">
-        <v>6984842</v>
+        <v>6984715</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,16 +907,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,7 +924,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123830363</v>
+        <v>123821283</v>
       </c>
       <c r="B4" t="n">
         <v>100279</v>
@@ -958,21 +958,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668042</v>
+        <v>668051</v>
       </c>
       <c r="R4" t="n">
-        <v>6984719</v>
+        <v>6984812</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123830174</v>
+        <v>123830363</v>
       </c>
       <c r="B5" t="n">
         <v>100279</v>
@@ -1091,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668067</v>
+        <v>668042</v>
       </c>
       <c r="R5" t="n">
-        <v>6984782</v>
+        <v>6984719</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123821176</v>
+        <v>123830564</v>
       </c>
       <c r="B6" t="n">
         <v>100279</v>
@@ -1216,7 +1211,7 @@
         <v>667999</v>
       </c>
       <c r="R6" t="n">
-        <v>6984703</v>
+        <v>6984717</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,6 +1264,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1285,7 +1285,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123821192</v>
+        <v>123830239</v>
       </c>
       <c r="B7" t="n">
         <v>100279</v>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668023</v>
+        <v>668068</v>
       </c>
       <c r="R7" t="n">
-        <v>6984811</v>
+        <v>6984751</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,12 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Granskog med inslag av lövträd. Blåsippa förekommande på merparten av m2 i skogen.</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,7 +1389,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Lågörtgranskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,7 +1407,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123830526</v>
+        <v>123830609</v>
       </c>
       <c r="B8" t="n">
         <v>100279</v>
@@ -1457,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668012</v>
+        <v>667970</v>
       </c>
       <c r="R8" t="n">
-        <v>6984748</v>
+        <v>6984746</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1492,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1497,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,7 +1529,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123830609</v>
+        <v>123821271</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1579,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>667970</v>
+        <v>668007</v>
       </c>
       <c r="R9" t="n">
-        <v>6984746</v>
+        <v>6984841</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1614,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1619,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,7 +1651,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123821271</v>
+        <v>123830526</v>
       </c>
       <c r="B10" t="n">
         <v>100279</v>
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668007</v>
+        <v>668012</v>
       </c>
       <c r="R10" t="n">
-        <v>6984841</v>
+        <v>6984748</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1736,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1741,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,7 +1773,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123830564</v>
+        <v>123830174</v>
       </c>
       <c r="B11" t="n">
         <v>100279</v>
@@ -1823,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>667999</v>
+        <v>668067</v>
       </c>
       <c r="R11" t="n">
-        <v>6984717</v>
+        <v>6984782</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1858,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123821283</v>
+        <v>123821223</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,38 +1907,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Sebäng, Ång</t>
+          <t>Sebäng 5:6, Omnesjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668051</v>
+        <v>668007</v>
       </c>
       <c r="R12" t="n">
-        <v>6984812</v>
+        <v>6984841</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1985,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,7 +2022,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123830239</v>
+        <v>123821176</v>
       </c>
       <c r="B13" t="n">
         <v>100279</v>
@@ -2062,10 +2067,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668068</v>
+        <v>667999</v>
       </c>
       <c r="R13" t="n">
-        <v>6984751</v>
+        <v>6984703</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2097,7 +2102,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2112,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,11 +2123,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2139,55 +2139,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123821223</v>
+        <v>123815157</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>95334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2808</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grov husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum pyrenaicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spruce) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sebäng 5:6, Omnesjön, Ång</t>
+          <t>Sebäng 5:6, Sebäng, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668007</v>
+        <v>668021</v>
       </c>
       <c r="R14" t="n">
-        <v>6984841</v>
+        <v>6984842</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2219,7 +2214,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,12 +2224,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Både färska och äldre spår på döende gran och högstubbe.</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,6 +2239,16 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
